--- a/produtos_ua.xlsx
+++ b/produtos_ua.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus_2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BA753BF-C819-497A-B8C0-47CFA2D1C246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEDFD3ED-C281-404D-A65B-9F32EDD58BE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30" yWindow="0" windowWidth="20460" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -353,9 +353,6 @@
     <t>UA IGNITE VI SL</t>
   </si>
   <si>
-    <t>33/34-45/46</t>
-  </si>
-  <si>
     <t>BKBKWT</t>
   </si>
   <si>
@@ -402,6 +399,9 @@
   </si>
   <si>
     <t>CHI</t>
+  </si>
+  <si>
+    <t>33/34 a 45/46</t>
   </si>
 </sst>
 </file>
@@ -870,6 +870,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AI66"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -878,7 +879,7 @@
     <col min="3" max="3" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.42578125" bestFit="1" customWidth="1"/>
@@ -997,7 +998,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="str">
         <f t="shared" ref="A2:A33" si="0">CONCATENATE(D2,"_",G2)</f>
         <v>6014730_BFDGFL</v>
@@ -1046,13 +1047,13 @@
         <v>41</v>
       </c>
       <c r="Q2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="3" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f t="shared" si="0"/>
         <v>6014730_SWSWEB</v>
@@ -1101,13 +1102,13 @@
         <v>41</v>
       </c>
       <c r="Q3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f t="shared" si="0"/>
         <v>6014730_BKBKMP</v>
@@ -1156,13 +1157,13 @@
         <v>41</v>
       </c>
       <c r="Q4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="5" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f t="shared" si="0"/>
         <v>6014730_BKBKTX</v>
@@ -1209,13 +1210,13 @@
         <v>41</v>
       </c>
       <c r="Q5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R5" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="6" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f t="shared" si="0"/>
         <v>6014732_SADTEB</v>
@@ -1264,13 +1265,13 @@
         <v>41</v>
       </c>
       <c r="Q6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R6" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f t="shared" si="0"/>
         <v>6014732_CABKBO</v>
@@ -1319,13 +1320,13 @@
         <v>41</v>
       </c>
       <c r="Q7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f t="shared" si="0"/>
         <v>6014732_BKCAMP</v>
@@ -1372,13 +1373,13 @@
         <v>41</v>
       </c>
       <c r="Q8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f t="shared" si="0"/>
         <v>6014732_BFDGFL</v>
@@ -1427,13 +1428,13 @@
         <v>41</v>
       </c>
       <c r="Q9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R9" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f t="shared" si="0"/>
         <v>6014732_WHPEPK</v>
@@ -1482,13 +1483,13 @@
         <v>41</v>
       </c>
       <c r="Q10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R10" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f t="shared" si="0"/>
         <v>6014736_BKBKCR</v>
@@ -1538,10 +1539,10 @@
         <v>41</v>
       </c>
       <c r="R11" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="12" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f t="shared" si="0"/>
         <v>6014736_RYRYWH</v>
@@ -1591,10 +1592,10 @@
         <v>41</v>
       </c>
       <c r="R12" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f t="shared" si="0"/>
         <v>6014736_STSTWH</v>
@@ -1644,10 +1645,10 @@
         <v>41</v>
       </c>
       <c r="R13" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f t="shared" si="0"/>
         <v>6014736_SGBKSG</v>
@@ -1699,10 +1700,10 @@
         <v>41</v>
       </c>
       <c r="R14" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f t="shared" si="0"/>
         <v>6006985_CACAMG</v>
@@ -1749,13 +1750,13 @@
         <v>41</v>
       </c>
       <c r="Q15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R15" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f t="shared" si="0"/>
         <v>6006985_CABKMS</v>
@@ -1802,13 +1803,13 @@
         <v>41</v>
       </c>
       <c r="Q16" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R16" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f t="shared" si="0"/>
         <v>6006985_FOFOBR</v>
@@ -1855,13 +1856,13 @@
         <v>41</v>
       </c>
       <c r="Q17" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R17" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f t="shared" si="0"/>
         <v>6006985_CRCRMP</v>
@@ -1910,13 +1911,13 @@
         <v>41</v>
       </c>
       <c r="Q18" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R18" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f t="shared" si="0"/>
         <v>6006985_MGMGBK</v>
@@ -1963,13 +1964,13 @@
         <v>41</v>
       </c>
       <c r="Q19" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R19" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f t="shared" si="0"/>
         <v>6006985_SWSWTU</v>
@@ -2016,13 +2017,13 @@
         <v>41</v>
       </c>
       <c r="Q20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R20" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f t="shared" si="0"/>
         <v>6006985_MGRAYB</v>
@@ -2071,13 +2072,13 @@
         <v>41</v>
       </c>
       <c r="Q21" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R21" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f t="shared" si="0"/>
         <v>6020667_ACBKDG</v>
@@ -2132,7 +2133,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f t="shared" si="0"/>
         <v>6020667_TITIBK</v>
@@ -2187,7 +2188,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f t="shared" si="0"/>
         <v>6020667_SWCKEB</v>
@@ -2242,7 +2243,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f t="shared" si="0"/>
         <v>6020667_BKMPMP</v>
@@ -2297,7 +2298,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f t="shared" si="0"/>
         <v>6020667_BKCAMP</v>
@@ -2352,7 +2353,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f t="shared" si="0"/>
         <v>6014744_BKBKMP</v>
@@ -2405,7 +2406,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f t="shared" si="0"/>
         <v>6014744_SGSGBK</v>
@@ -2458,7 +2459,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f t="shared" si="0"/>
         <v>6014744_AGAGWH</v>
@@ -2511,7 +2512,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f t="shared" si="0"/>
         <v>6014744_BNBKMP</v>
@@ -2566,7 +2567,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f t="shared" si="0"/>
         <v>6014744_CASBMG</v>
@@ -2621,7 +2622,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
         <f t="shared" si="0"/>
         <v>6014744_APAPPP</v>
@@ -2676,7 +2677,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
         <f t="shared" si="0"/>
         <v>6020665_BKBKMP</v>
@@ -2731,7 +2732,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
         <f t="shared" ref="A34:A66" si="1">CONCATENATE(D34,"_",G34)</f>
         <v>6020665_CRCRMP</v>
@@ -2786,7 +2787,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="str">
         <f t="shared" si="1"/>
         <v>6020665_MGMOMP</v>
@@ -2841,7 +2842,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="str">
         <f t="shared" si="1"/>
         <v>6020665_ACACMP</v>
@@ -2896,7 +2897,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="str">
         <f t="shared" si="1"/>
         <v>6020665_SWSWCK</v>
@@ -2951,7 +2952,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="str">
         <f t="shared" si="1"/>
         <v>6014745_CRFGVR</v>
@@ -2995,16 +2996,16 @@
         <v>41</v>
       </c>
       <c r="P38" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q38" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R38" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="str">
         <f t="shared" si="1"/>
         <v>6014745_FGLLPP</v>
@@ -3048,16 +3049,16 @@
         <v>41</v>
       </c>
       <c r="P39" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q39" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R39" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="str">
         <f t="shared" si="1"/>
         <v>6014745_BKCABK</v>
@@ -3103,16 +3104,16 @@
         <v>41</v>
       </c>
       <c r="P40" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q40" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R40" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="str">
         <f t="shared" si="1"/>
         <v>6020660_MOGBGC</v>
@@ -3161,13 +3162,13 @@
         <v>41</v>
       </c>
       <c r="Q41" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R41" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="str">
         <f t="shared" si="1"/>
         <v>6020660_VVVVLC</v>
@@ -3216,13 +3217,13 @@
         <v>41</v>
       </c>
       <c r="Q42" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R42" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="str">
         <f t="shared" si="1"/>
         <v>6020660_SWSWPP</v>
@@ -3271,13 +3272,13 @@
         <v>41</v>
       </c>
       <c r="Q43" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R43" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="str">
         <f t="shared" si="1"/>
         <v>6020660_BKRRSA</v>
@@ -3326,13 +3327,13 @@
         <v>41</v>
       </c>
       <c r="Q44" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R44" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="str">
         <f t="shared" si="1"/>
         <v>6020660_SWSWBN</v>
@@ -3381,13 +3382,13 @@
         <v>41</v>
       </c>
       <c r="Q45" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R45" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="str">
         <f t="shared" si="1"/>
         <v>6020660_BLKBKW</v>
@@ -3436,13 +3437,13 @@
         <v>41</v>
       </c>
       <c r="Q46" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R46" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="str">
         <f t="shared" si="1"/>
         <v>6014748_MPPCTX</v>
@@ -3497,7 +3498,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="str">
         <f t="shared" si="1"/>
         <v>6014748_WMTGBK</v>
@@ -3550,7 +3551,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="str">
         <f t="shared" si="1"/>
         <v>6014748_BKCAWH</v>
@@ -3605,7 +3606,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="str">
         <f t="shared" si="1"/>
         <v>6020662_BKGMPU</v>
@@ -3654,13 +3655,13 @@
         <v>41</v>
       </c>
       <c r="Q50" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R50" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="str">
         <f t="shared" si="1"/>
         <v>6020662_BKWHPU</v>
@@ -3709,13 +3710,13 @@
         <v>41</v>
       </c>
       <c r="Q51" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R51" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="str">
         <f t="shared" si="1"/>
         <v>6020662_WHMGWT</v>
@@ -3764,10 +3765,10 @@
         <v>41</v>
       </c>
       <c r="Q52" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R52" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
@@ -3776,7 +3777,7 @@
         <v>3025902_BKBKWT</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C53" t="s">
         <v>103</v>
@@ -3788,10 +3789,10 @@
         <v>104</v>
       </c>
       <c r="F53" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G53" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>40</v>
@@ -3829,7 +3830,7 @@
         <v>3025902_WHWHBA</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C54" t="s">
         <v>103</v>
@@ -3841,10 +3842,10 @@
         <v>104</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H54" s="1" t="s">
         <v>40</v>
@@ -3882,7 +3883,7 @@
         <v>3027787_WTWTBK</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C55" t="s">
         <v>103</v>
@@ -3891,13 +3892,13 @@
         <v>3027787</v>
       </c>
       <c r="E55" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G55" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>109</v>
       </c>
       <c r="H55" s="1" t="s">
         <v>40</v>
@@ -3935,7 +3936,7 @@
         <v>3027787_BLKBKW</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C56" t="s">
         <v>103</v>
@@ -3944,10 +3945,10 @@
         <v>3027787</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>92</v>
@@ -3988,7 +3989,7 @@
         <v>6006999_MNYDWG</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C57" t="s">
         <v>103</v>
@@ -3997,13 +3998,13 @@
         <v>6006999</v>
       </c>
       <c r="E57" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G57" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>111</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>40</v>
@@ -4041,7 +4042,7 @@
         <v>6006999_WTBKBK</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C58" t="s">
         <v>103</v>
@@ -4050,13 +4051,13 @@
         <v>6006999</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H58" s="1" t="s">
         <v>40</v>
@@ -4094,7 +4095,7 @@
         <v>6006999_BLKBKW</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C59" t="s">
         <v>103</v>
@@ -4103,10 +4104,10 @@
         <v>6006999</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>92</v>
@@ -4141,7 +4142,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="str">
         <f t="shared" si="1"/>
         <v>6020663_WHPPPE</v>
@@ -4156,13 +4157,13 @@
         <v>6020663</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>50</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H60" s="1" t="s">
         <v>52</v>
@@ -4178,7 +4179,7 @@
         <v>42</v>
       </c>
       <c r="M60" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="N60" t="s">
         <v>41</v>
@@ -4196,7 +4197,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="str">
         <f t="shared" si="1"/>
         <v>6020663_BFBFBF</v>
@@ -4211,13 +4212,13 @@
         <v>6020663</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>50</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H61" s="1" t="s">
         <v>52</v>
@@ -4233,7 +4234,7 @@
         <v>42</v>
       </c>
       <c r="M61" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="N61" t="s">
         <v>41</v>
@@ -4251,7 +4252,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="str">
         <f t="shared" si="1"/>
         <v>6020663_TITIPP</v>
@@ -4266,13 +4267,13 @@
         <v>6020663</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>50</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H62" s="1" t="s">
         <v>52</v>
@@ -4288,7 +4289,7 @@
         <v>42</v>
       </c>
       <c r="M62" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="N62" t="s">
         <v>41</v>
@@ -4306,7 +4307,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="str">
         <f t="shared" si="1"/>
         <v>6020663_SARPBR</v>
@@ -4321,13 +4322,13 @@
         <v>6020663</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>50</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H63" s="1" t="s">
         <v>52</v>
@@ -4343,7 +4344,7 @@
         <v>42</v>
       </c>
       <c r="M63" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="N63" t="s">
         <v>41</v>
@@ -4361,7 +4362,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="str">
         <f t="shared" si="1"/>
         <v>6020663_BKMTSC</v>
@@ -4376,13 +4377,13 @@
         <v>6020663</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>50</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H64" s="1" t="s">
         <v>52</v>
@@ -4398,7 +4399,7 @@
         <v>42</v>
       </c>
       <c r="M64" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="N64" t="s">
         <v>41</v>
@@ -4422,7 +4423,7 @@
         <v>3027786_BLKBKW</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C65" t="s">
         <v>103</v>
@@ -4431,10 +4432,10 @@
         <v>3027786</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>92</v>
@@ -4475,7 +4476,7 @@
         <v>3027786_WTWTBK</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C66" t="s">
         <v>103</v>
@@ -4484,13 +4485,13 @@
         <v>3027786</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H66" s="1" t="s">
         <v>40</v>
@@ -4523,7 +4524,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AI66" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:AI66" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="CHI"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>